--- a/assets/4/db.xlsx
+++ b/assets/4/db.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
   <si>
     <t>№</t>
   </si>
@@ -40,6 +40,138 @@
   </si>
   <si>
     <t>ответ</t>
+  </si>
+  <si>
+    <t>Автобус — общественный транспорт, поэтому он проедет первым</t>
+  </si>
+  <si>
+    <t>Автобус проедет последним</t>
+  </si>
+  <si>
+    <t>Я проеду первым!</t>
+  </si>
+  <si>
+    <t>Я и грузовик находимся на главной дороге</t>
+  </si>
+  <si>
+    <t>Автомобиль справа поедет первым</t>
+  </si>
+  <si>
+    <t>Я не тороплюсь и проеду последним</t>
+  </si>
+  <si>
+    <t>Знак дополнительной информации показывает направление главной дороги</t>
+  </si>
+  <si>
+    <t>Я должен остановиться, поставить ногу на асфальт, дать проехать грузовику</t>
+  </si>
+  <si>
+    <t>Я проеду последним</t>
+  </si>
+  <si>
+    <t>Желтый автомобиль меня пропустит</t>
+  </si>
+  <si>
+    <t>Я уступлю дорогу всем автомобилям</t>
+  </si>
+  <si>
+    <t>Нет, встречный автомобиль уступит мне дорогу</t>
+  </si>
+  <si>
+    <t>Я должен остановиться, поставить ногу на асфальт и проехать только прямо</t>
+  </si>
+  <si>
+    <t>Я могу проехать прямо и направо</t>
+  </si>
+  <si>
+    <t>Я должен пропустить оба автомобиля</t>
+  </si>
+  <si>
+    <t>Автобус пропустит меня</t>
+  </si>
+  <si>
+    <t>Автобус проедет первым. Для него горит основной зеленый сигнал светофора</t>
+  </si>
+  <si>
+    <t>Грузовик проедет после меня</t>
+  </si>
+  <si>
+    <t>Грузовику запрещено пересекать велосипедную дорожку</t>
+  </si>
+  <si>
+    <t>Мне разрешено повернуть направо и выехать с велосипедной дорожки. Я пропущу грузовик</t>
+  </si>
+  <si>
+    <t>Я пропущу пешеходов и проеду сам</t>
+  </si>
+  <si>
+    <t>Я уступлю дорогу только пешеходу справа</t>
+  </si>
+  <si>
+    <t>Пешеходы должны пропустить меня</t>
+  </si>
+  <si>
+    <t>Я могу проехать на зеленый сигнал светофора</t>
+  </si>
+  <si>
+    <t>Автомобиль скорой помощи проедет перекресток, соблюдая сигнал регулировщика</t>
+  </si>
+  <si>
+    <t>Движение обоим пешеходам запрещено!</t>
+  </si>
+  <si>
+    <t>Только пешеход в красной куртке может переходить дорогу</t>
+  </si>
+  <si>
+    <t>Регулировщик не регулирует движение пешеходов</t>
+  </si>
+  <si>
+    <t>Убери лишние фрагменты, которые не относятся к основной картинке</t>
+  </si>
+  <si>
+    <t>Б и Г</t>
+  </si>
+  <si>
+    <t>А и В</t>
+  </si>
+  <si>
+    <t>А и Г</t>
+  </si>
+  <si>
+    <t>Внимательно посмотри на картинки. Отметь нарушителей</t>
+  </si>
+  <si>
+    <t>Только А</t>
+  </si>
+  <si>
+    <t>Б и В</t>
+  </si>
+  <si>
+    <t>Только Б</t>
+  </si>
+  <si>
+    <t>А и Б</t>
+  </si>
+  <si>
+    <t>В и Г</t>
+  </si>
+  <si>
+    <t>Знак «Пешеходная зона» относится к группе знаков особых предписаний</t>
+  </si>
+  <si>
+    <t>Знак  «Пешеходная зона» разрешает движение велосипедистов на данном участке</t>
+  </si>
+  <si>
+    <t>Этот знак запрещает пешеходам движение</t>
+  </si>
+  <si>
+    <t>Этот знак называется «Пешеходная дорожка»</t>
+  </si>
+  <si>
+    <t>Этот знак называется «Пешеходный переход»</t>
+  </si>
+  <si>
+    <t>Этот знак относится к группе информационных знаков</t>
   </si>
 </sst>
 </file>
@@ -414,6 +546,15 @@
       <c r="B2">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -422,6 +563,15 @@
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -430,6 +580,15 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -438,6 +597,15 @@
       <c r="B5">
         <v>2</v>
       </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -446,6 +614,15 @@
       <c r="B6">
         <v>1</v>
       </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -454,6 +631,15 @@
       <c r="B7">
         <v>2</v>
       </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -462,6 +648,15 @@
       <c r="B8">
         <v>3</v>
       </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -470,6 +665,15 @@
       <c r="B9">
         <v>1</v>
       </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -478,6 +682,15 @@
       <c r="B10">
         <v>1</v>
       </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -486,6 +699,15 @@
       <c r="B11">
         <v>2</v>
       </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -494,6 +716,18 @@
       <c r="B12">
         <v>1</v>
       </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -502,6 +736,18 @@
       <c r="B13">
         <v>1</v>
       </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -510,6 +756,21 @@
       <c r="B14">
         <v>2</v>
       </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -518,6 +779,21 @@
       <c r="B15">
         <v>2</v>
       </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -526,29 +802,77 @@
       <c r="B16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
